--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121641481</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286256</v>
+        <v>122286255</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4K+</t>
+          <t>4K</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -863,17 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Storck</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286255</v>
+        <v>122286256</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4K</t>
+          <t>4K+</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -863,12 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +893,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Johan Storck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286256</v>
+        <v>122286255</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>57295</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4K+</t>
+          <t>4K</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -863,17 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Storck</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286255</v>
+        <v>122286256</v>
       </c>
       <c r="B3" t="n">
         <v>57295</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4K</t>
+          <t>4K+</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -863,12 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +893,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Johan Storck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286256</v>
+        <v>122286255</v>
       </c>
       <c r="B3" t="n">
         <v>57295</v>
@@ -795,11 +795,6 @@
       <c r="E3" t="n">
         <v>100067</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Haliaeetus albicilla</t>
@@ -817,7 +812,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4K+</t>
+          <t>4K</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -863,17 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +883,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Storck</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286255</v>
+        <v>122286256</v>
       </c>
       <c r="B3" t="n">
-        <v>57295</v>
+        <v>57299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,6 +795,11 @@
       <c r="E3" t="n">
         <v>100067</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Haliaeetus albicilla</t>
@@ -812,7 +817,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4K</t>
+          <t>4K+</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -858,12 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,7 +893,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Johan Storck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286256</v>
+        <v>122286255</v>
       </c>
       <c r="B3" t="n">
         <v>57299</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4K+</t>
+          <t>4K</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -863,17 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Storck</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286255</v>
+        <v>122286256</v>
       </c>
       <c r="B3" t="n">
         <v>57299</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4K</t>
+          <t>4K+</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -863,12 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +893,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Johan Storck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>122286256</v>
       </c>
       <c r="B3" t="n">
-        <v>57299</v>
+        <v>57300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121641481</v>
+        <v>122286255</v>
       </c>
       <c r="B2" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,24 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långhult, Sm</t>
@@ -745,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,63 +781,42 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Nina Marliden</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122286256</v>
+        <v>121641481</v>
       </c>
       <c r="B3" t="n">
-        <v>57300</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>4K+</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långhult, Sm</t>
@@ -863,17 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Subadult. Glidflygande innan den tog termik och fortsatte</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +878,107 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Storck</t>
+          <t>Ellen Hultman, Nina Marliden</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121641482</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>429076</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6385450</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gislaved</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stengårdshult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ellen Hultman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ellen Hultman, Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15227-2024 artfynd.xlsx
+++ b/artfynd/A 15227-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122286255</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121641481</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,8 +994,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121641482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>